--- a/mlef_pipeline/results/DCR/HIGH_PDL1/RWD_DP_PYRAD/results.xlsx
+++ b/mlef_pipeline/results/DCR/HIGH_PDL1/RWD_DP_PYRAD/results.xlsx
@@ -468,22 +468,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.82 ± 0.09</t>
+          <t>0.81 ± 0.09</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.72 ± 0.10</t>
+          <t>0.71 ± 0.12</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.83 ± 0.18</t>
+          <t>0.77 ± 0.16</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.67 ± 0.21</t>
+          <t>0.70 ± 0.20</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -498,7 +498,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.48 ± 0.34</t>
+          <t>0.42 ± 0.34</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -528,22 +528,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.69 ± 0.25</t>
+          <t>0.65 ± 0.26</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="F4" t="n">
